--- a/survey_templates/041_job_satisfaction_survey--survey_templates.xlsx
+++ b/survey_templates/041_job_satisfaction_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
